--- a/data/usuarios.xlsx
+++ b/data/usuarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\analisjr_operaciones.PROMEDICO\Documents\portal-fondo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBA60C2C-E491-4196-B750-6472D40047DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB21938B-A3B1-46D0-B04C-A206E58F3130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E16C787A-64FB-4010-BF0B-7D4A9D0FC4E2}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="21270" windowHeight="15585" xr2:uid="{E16C787A-64FB-4010-BF0B-7D4A9D0FC4E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,12 +38,66 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>cedula</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>correo</t>
+  </si>
+  <si>
+    <t>clave_hash</t>
+  </si>
+  <si>
+    <t>perfil</t>
+  </si>
+  <si>
+    <t>activo</t>
+  </si>
+  <si>
+    <t>cambiar_clave</t>
+  </si>
+  <si>
+    <t>Administrador</t>
+  </si>
+  <si>
+    <t>jaider700200@gmail.com</t>
+  </si>
+  <si>
+    <t>admin123</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,13 +120,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -405,9 +465,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05F5F91-38F9-4BFC-BD40-C53E4C6183C8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="7" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{F34DD70D-978B-4BA4-BEC7-6F512F1560BC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>